--- a/Team-Data/2011-12/4-20-2011-12.xlsx
+++ b/Team-Data/2011-12/4-20-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
         <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.603</v>
+        <v>0.597</v>
       </c>
       <c r="H2" t="n">
         <v>49</v>
@@ -679,34 +746,34 @@
         <v>36.5</v>
       </c>
       <c r="J2" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L2" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M2" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N2" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O2" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P2" t="n">
         <v>21.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="R2" t="n">
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T2" t="n">
         <v>41.3</v>
@@ -715,19 +782,19 @@
         <v>22.3</v>
       </c>
       <c r="V2" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W2" t="n">
         <v>8.1</v>
       </c>
       <c r="X2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
         <v>19.3</v>
@@ -739,7 +806,7 @@
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>8</v>
@@ -754,13 +821,13 @@
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
         <v>9</v>
@@ -769,7 +836,7 @@
         <v>12</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -793,16 +860,16 @@
         <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -811,7 +878,7 @@
         <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" t="n">
         <v>37</v>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>0.578</v>
+        <v>0.587</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
@@ -861,10 +928,10 @@
         <v>35.5</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L3" t="n">
         <v>5.5</v>
@@ -873,34 +940,34 @@
         <v>14.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O3" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="R3" t="n">
         <v>7.8</v>
       </c>
       <c r="S3" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="U3" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V3" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W3" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X3" t="n">
         <v>5.5</v>
@@ -912,28 +979,28 @@
         <v>20.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="AB3" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF3" t="n">
         <v>10</v>
       </c>
-      <c r="AF3" t="n">
-        <v>11</v>
-      </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -954,10 +1021,10 @@
         <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>5</v>
@@ -972,25 +1039,25 @@
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
         <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BB3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>0.113</v>
+        <v>0.115</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
@@ -1043,7 +1110,7 @@
         <v>33.3</v>
       </c>
       <c r="J4" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K4" t="n">
         <v>0.414</v>
@@ -1055,13 +1122,13 @@
         <v>13.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.297</v>
+        <v>0.296</v>
       </c>
       <c r="O4" t="n">
         <v>16.5</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0.747</v>
@@ -1076,13 +1143,13 @@
         <v>39</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W4" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X4" t="n">
         <v>5.4</v>
@@ -1091,19 +1158,19 @@
         <v>5.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA4" t="n">
         <v>20.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>87.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13.5</v>
+        <v>-13.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1157,7 +1224,7 @@
         <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1297,19 +1364,19 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ5" t="n">
         <v>7</v>
       </c>
       <c r="AK5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM5" t="n">
         <v>19</v>
@@ -1318,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
         <v>20</v>
@@ -1336,10 +1403,10 @@
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -1389,58 +1456,58 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>0.339</v>
+        <v>0.328</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="J6" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.423</v>
+        <v>0.422</v>
       </c>
       <c r="L6" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
         <v>19.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
         <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.718</v>
+        <v>0.717</v>
       </c>
       <c r="R6" t="n">
         <v>12.7</v>
       </c>
       <c r="S6" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T6" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
         <v>15.5</v>
@@ -1455,7 +1522,7 @@
         <v>6.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
         <v>21.1</v>
@@ -1464,10 +1531,10 @@
         <v>93.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>-6.6</v>
+        <v>-6.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
@@ -1497,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1638,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H7" t="n">
         <v>48.7</v>
       </c>
       <c r="I7" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
         <v>82.09999999999999</v>
@@ -1595,31 +1662,31 @@
         <v>0.444</v>
       </c>
       <c r="L7" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M7" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="O7" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P7" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.769</v>
+        <v>0.765</v>
       </c>
       <c r="R7" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T7" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U7" t="n">
         <v>21.1</v>
@@ -1634,25 +1701,25 @@
         <v>5.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z7" t="n">
         <v>18.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -1661,7 +1728,7 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
         <v>18</v>
@@ -1673,7 +1740,7 @@
         <v>19</v>
       </c>
       <c r="AL7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM7" t="n">
         <v>4</v>
@@ -1682,10 +1749,10 @@
         <v>19</v>
       </c>
       <c r="AO7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ7" t="n">
         <v>12</v>
@@ -1694,16 +1761,16 @@
         <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -1721,7 +1788,7 @@
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
         <v>15</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
         <v>13</v>
@@ -1882,7 +1949,7 @@
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV8" t="n">
         <v>27</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>-5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
         <v>22</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -2117,61 +2184,61 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="H10" t="n">
         <v>48.2</v>
       </c>
       <c r="I10" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J10" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>0.457</v>
       </c>
       <c r="L10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M10" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>0.39</v>
+        <v>0.389</v>
       </c>
       <c r="O10" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="P10" t="n">
         <v>19</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.771</v>
+        <v>0.775</v>
       </c>
       <c r="R10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S10" t="n">
         <v>29.4</v>
       </c>
       <c r="T10" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="U10" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V10" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W10" t="n">
         <v>8.1</v>
@@ -2189,13 +2256,13 @@
         <v>16.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2210,7 +2277,7 @@
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
         <v>9</v>
@@ -2234,7 +2301,7 @@
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
@@ -2249,16 +2316,16 @@
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>17</v>
@@ -2398,19 +2465,19 @@
         <v>3</v>
       </c>
       <c r="AK11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL11" t="n">
         <v>10</v>
       </c>
       <c r="AM11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AN11" t="n">
         <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>28</v>
@@ -2425,7 +2492,7 @@
         <v>18</v>
       </c>
       <c r="AT11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU11" t="n">
         <v>12</v>
@@ -2446,7 +2513,7 @@
         <v>23</v>
       </c>
       <c r="BA11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2574,10 +2641,10 @@
         <v>9</v>
       </c>
       <c r="AI12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK12" t="n">
         <v>23</v>
@@ -2619,7 +2686,7 @@
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
       </c>
       <c r="AF13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG13" t="n">
         <v>7</v>
@@ -2771,10 +2838,10 @@
         <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -2786,7 +2853,7 @@
         <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT13" t="n">
         <v>18</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -2845,28 +2912,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
         <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>0.625</v>
+        <v>0.635</v>
       </c>
       <c r="H14" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I14" t="n">
         <v>36.7</v>
       </c>
       <c r="J14" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L14" t="n">
         <v>5.5</v>
@@ -2875,25 +2942,25 @@
         <v>16.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.324</v>
+        <v>0.322</v>
       </c>
       <c r="O14" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P14" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R14" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S14" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="T14" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="U14" t="n">
         <v>22.4</v>
@@ -2911,19 +2978,19 @@
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB14" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2962,7 +3029,7 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>11</v>
@@ -2998,7 +3065,7 @@
         <v>16</v>
       </c>
       <c r="BC14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -3027,34 +3094,34 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>0.603</v>
+        <v>0.597</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J15" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K15" t="n">
         <v>0.447</v>
       </c>
       <c r="L15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M15" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="N15" t="n">
         <v>0.33</v>
@@ -3066,7 +3133,7 @@
         <v>22.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R15" t="n">
         <v>12.5</v>
@@ -3078,10 +3145,10 @@
         <v>42</v>
       </c>
       <c r="U15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V15" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W15" t="n">
         <v>9.6</v>
@@ -3099,13 +3166,13 @@
         <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>94.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC15" t="n">
         <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>8</v>
@@ -3117,13 +3184,13 @@
         <v>8</v>
       </c>
       <c r="AH15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
         <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK15" t="n">
         <v>16</v>
@@ -3135,7 +3202,7 @@
         <v>28</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO15" t="n">
         <v>10</v>
@@ -3144,10 +3211,10 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS15" t="n">
         <v>26</v>
@@ -3174,13 +3241,13 @@
         <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB15" t="n">
         <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>7</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>3</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
         <v>5</v>
@@ -3308,7 +3375,7 @@
         <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL16" t="n">
         <v>20</v>
@@ -3317,7 +3384,7 @@
         <v>23</v>
       </c>
       <c r="AN16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO16" t="n">
         <v>5</v>
@@ -3326,7 +3393,7 @@
         <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>0.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3493,7 +3560,7 @@
         <v>18</v>
       </c>
       <c r="AL17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM17" t="n">
         <v>16</v>
@@ -3517,10 +3584,10 @@
         <v>23</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
         <v>6</v>
@@ -3538,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -3663,13 +3730,13 @@
         <v>21</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
         <v>20</v>
       </c>
       <c r="AJ18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>23</v>
@@ -3896,7 +3963,7 @@
         <v>29</v>
       </c>
       <c r="AY19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ19" t="n">
         <v>12</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -4015,19 +4082,19 @@
         <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4072,10 +4139,10 @@
         <v>26</v>
       </c>
       <c r="AW20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX20" t="n">
         <v>21</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>22</v>
       </c>
       <c r="AY20" t="n">
         <v>25</v>
@@ -4084,7 +4151,7 @@
         <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
         <v>33</v>
       </c>
       <c r="F21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>0.524</v>
+        <v>0.532</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4137,7 +4204,7 @@
         <v>35.6</v>
       </c>
       <c r="J21" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K21" t="n">
         <v>0.44</v>
@@ -4146,37 +4213,37 @@
         <v>7.7</v>
       </c>
       <c r="M21" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="O21" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P21" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R21" t="n">
         <v>11.5</v>
       </c>
       <c r="S21" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="T21" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U21" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V21" t="n">
         <v>16.2</v>
       </c>
       <c r="W21" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X21" t="n">
         <v>4.2</v>
@@ -4185,19 +4252,19 @@
         <v>5</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
         <v>14</v>
@@ -4209,7 +4276,7 @@
         <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4221,22 +4288,22 @@
         <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM21" t="n">
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO21" t="n">
         <v>7</v>
       </c>
       <c r="AP21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
         <v>15</v>
@@ -4245,7 +4312,7 @@
         <v>17</v>
       </c>
       <c r="AT21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
         <v>23</v>
@@ -4269,7 +4336,7 @@
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
         <v>8</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -4301,52 +4368,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
         <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.73</v>
+        <v>0.726</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J22" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L22" t="n">
         <v>7.1</v>
       </c>
       <c r="M22" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="N22" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O22" t="n">
         <v>21.2</v>
       </c>
       <c r="P22" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="Q22" t="n">
         <v>0.802</v>
       </c>
       <c r="R22" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S22" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T22" t="n">
         <v>43.6</v>
@@ -4367,19 +4434,19 @@
         <v>4.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB22" t="n">
         <v>102.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4406,10 +4473,10 @@
         <v>12</v>
       </c>
       <c r="AM22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4424,7 +4491,7 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
         <v>22</v>
@@ -4451,10 +4518,10 @@
         <v>11</v>
       </c>
       <c r="BB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC22" t="n">
         <v>3</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>1.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE23" t="n">
         <v>11</v>
@@ -4570,10 +4637,10 @@
         <v>10</v>
       </c>
       <c r="AG23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -4743,19 +4810,19 @@
         <v>4.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>17</v>
       </c>
       <c r="AF24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG24" t="n">
         <v>17</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
         <v>9</v>
@@ -4782,13 +4849,13 @@
         <v>30</v>
       </c>
       <c r="AQ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR24" t="n">
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT24" t="n">
         <v>8</v>
@@ -4806,7 +4873,7 @@
         <v>14</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -4925,22 +4992,22 @@
         <v>0.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ25" t="n">
         <v>13</v>
@@ -4979,7 +5046,7 @@
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -5137,13 +5204,13 @@
         <v>9</v>
       </c>
       <c r="AN26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
@@ -5161,7 +5228,7 @@
         <v>17</v>
       </c>
       <c r="AV26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW26" t="n">
         <v>13</v>
@@ -5179,7 +5246,7 @@
         <v>14</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" t="n">
         <v>20</v>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G27" t="n">
-        <v>0.317</v>
+        <v>0.323</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
@@ -5229,28 +5296,28 @@
         <v>37.3</v>
       </c>
       <c r="J27" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.431</v>
+        <v>0.432</v>
       </c>
       <c r="L27" t="n">
         <v>6.3</v>
       </c>
       <c r="M27" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N27" t="n">
         <v>0.316</v>
       </c>
       <c r="O27" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P27" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.736</v>
+        <v>0.737</v>
       </c>
       <c r="R27" t="n">
         <v>13.5</v>
@@ -5268,31 +5335,31 @@
         <v>14.7</v>
       </c>
       <c r="W27" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X27" t="n">
         <v>4.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
         <v>19.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
         <v>27</v>
@@ -5313,7 +5380,7 @@
         <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM27" t="n">
         <v>11</v>
@@ -5322,7 +5389,7 @@
         <v>29</v>
       </c>
       <c r="AO27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP27" t="n">
         <v>10</v>
@@ -5334,7 +5401,7 @@
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
         <v>9</v>
@@ -5349,16 +5416,16 @@
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
         <v>9</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.742</v>
+        <v>0.738</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J28" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.476</v>
+        <v>0.474</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.393</v>
+        <v>0.39</v>
       </c>
       <c r="O28" t="n">
         <v>16</v>
@@ -5432,7 +5499,7 @@
         <v>21.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.744</v>
+        <v>0.741</v>
       </c>
       <c r="R28" t="n">
         <v>10.3</v>
@@ -5465,13 +5532,13 @@
         <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>103</v>
+        <v>102.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5492,7 +5559,7 @@
         <v>8</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL28" t="n">
         <v>2</v>
@@ -5507,10 +5574,10 @@
         <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5519,10 +5586,10 @@
         <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>3</v>
@@ -5534,7 +5601,7 @@
         <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ28" t="n">
         <v>3</v>
@@ -5543,10 +5610,10 @@
         <v>21</v>
       </c>
       <c r="BB28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB29" t="n">
         <v>27</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>0.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>14</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH30" t="n">
         <v>2</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6050,7 +6117,7 @@
         <v>27</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP31" t="n">
         <v>22</v>
@@ -6080,7 +6147,7 @@
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-20-2011-12</t>
+          <t>2012-04-20</t>
         </is>
       </c>
     </row>
